--- a/Docs/NonameProtocol.xlsx
+++ b/Docs/NonameProtocol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Code\NRD-W300-V1\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Development\01_Source\Neurodyne\NRD-W300-V1\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF202B2A-29C4-4DF4-AB06-2962C6BF1EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10A77A9-9B09-4D06-88D7-ACEFB1EDD36D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{B534FB32-8458-43B0-8E27-FBD0753503E0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16770" activeTab="1" xr2:uid="{B534FB32-8458-43B0-8E27-FBD0753503E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="196">
   <si>
     <t>BYTE0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +126,654 @@
   </si>
   <si>
     <t>Update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x81</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start Motor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정 값을 기준으로 모터 동작 On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host &gt;&gt; Motor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Motor &gt;&gt; Host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RESULT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stop Motor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정 값을 기준으로 모터 동작 Off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전송되는 파라미터를 기준으로 토크 제어 모드로 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Torque0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Torque1</t>
+  </si>
+  <si>
+    <t>Torque2</t>
+  </si>
+  <si>
+    <t>Torque3</t>
+  </si>
+  <si>
+    <t>Time0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time1</t>
+  </si>
+  <si>
+    <t>Time2</t>
+  </si>
+  <si>
+    <t>전송되는 파라미터를 기준으로 속도 제어 모드로 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x84</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed1</t>
+  </si>
+  <si>
+    <t>Speed2</t>
+  </si>
+  <si>
+    <t>Speed3</t>
+  </si>
+  <si>
+    <t>전송되는 파라미터를 기준으로 위치 제어 모드로 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position1</t>
+  </si>
+  <si>
+    <t>Position2</t>
+  </si>
+  <si>
+    <t>Position3</t>
+  </si>
+  <si>
+    <t>0x85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 수행 중인 제어모드 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set Parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get Parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reset Parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set Parameter as Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x94</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control Commands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Command Protocol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Configuration Commands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Configuration 명령어 패킷 구성은 다음과 같다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. ParamID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. ParamType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Data(4Bytes)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. ParamID(1Byte)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. ParamType(1Byte)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAN ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x02</t>
+  </si>
+  <si>
+    <t>0x03</t>
+  </si>
+  <si>
+    <t>0x04</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>0x08</t>
+  </si>
+  <si>
+    <t>0x09</t>
+  </si>
+  <si>
+    <t>0x0A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output shaft Zero Position</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAN Baud Rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reserved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KP of Current Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KI of Current Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KP of Speed Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KI of Speed Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KP of Position Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KI of Position Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KD of Position Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Learning Rate of Speed Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Learning Rate of Position Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32-bit float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32-bit signed integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x9x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA1</t>
+  </si>
+  <si>
+    <t>DATA2</t>
+  </si>
+  <si>
+    <t>DATA3</t>
+  </si>
+  <si>
+    <t>Value = (float)Value;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value = ((int32_t)DATA0 | ((int32_t)DATA1&lt;&lt;8) | ((int32_t)DATA1&lt;&lt;16) | ((int32_t)DATA1&lt;&lt;24));</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if ParamType == 32-bit signed integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if ParamType == 32-bit float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파라미터 ID에 따른 값을 모터에 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파라미터 ID에 따른 모터 설정값을 받음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파라미터 ID에 따른 모터의 Default 값을 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파라미터 ID에 따른 모터 설정값을 Default 값으로 초기화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x94</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request Status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request Speed Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request Position Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request PST(Pos/Spd/Cur) Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Status Commands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request Status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터의 현재 상태를 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>State ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StateID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Error (ErrorCode 참조, DATA0~DATA3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ready</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerSave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터의 토크 값을 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request Torque Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터의 속도 값을 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터의 위치 값을 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request PST Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터의 위치/속도/토크 값을 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA4</t>
+  </si>
+  <si>
+    <t>DATA5</t>
+  </si>
+  <si>
+    <t>Firmware Update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xB1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -144,7 +781,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,13 +805,55 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -206,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -216,11 +895,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,91 +1262,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D2795-F3D1-4BB4-870C-3DA182DEFD01}">
-  <dimension ref="B3:D12"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="B4:D20"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="15.69921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.69921875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="5.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="4" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D4" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C5" s="1" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C6" s="1" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C7" s="1" t="s">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C8" s="1" t="s">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C9" s="1" t="s">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B12" s="1" t="s">
+      <c r="C15" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -651,57 +1443,3233 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425A190A-1216-4FBC-A23C-CC9D93A51BC6}">
-  <dimension ref="B5:I6"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:I284"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="9" width="10.69921875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="5.625" style="1" customWidth="1"/>
+    <col min="2" max="9" width="10.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="2" t="s">
+    <row r="2" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="2" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="11" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+    </row>
+    <row r="78" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B84" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B98" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B100" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B102" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B103" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B104" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B105" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B106" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B107" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B108" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B109" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B110" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B111" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B112" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B113" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B114" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B115" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B116" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B117" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B118" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B119" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B120" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B121" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B122" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B123" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B124" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B125" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B126" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B127" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B128" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B129" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B130" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B131" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B132" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B133" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B134" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B135" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B136" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B137" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B138" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B139" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B140" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B141" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D141" s="12"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B142" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D142" s="12"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B143" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D143" s="12"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B144" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D144" s="12"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B145" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D145" s="12"/>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B146" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D146" s="12"/>
+      <c r="E146" s="12"/>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B147" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D147" s="12"/>
+      <c r="E147" s="12"/>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B148" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D148" s="12"/>
+      <c r="E148" s="12"/>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B149" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D149" s="12"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B150" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D150" s="12"/>
+      <c r="E150" s="12"/>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B151" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B154" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B155" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B156" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D156" s="12"/>
+      <c r="E156" s="12"/>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B157" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D157" s="12"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B160" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B161" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B162" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B164" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B165" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B166" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B169" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B170" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B171" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B172" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B173" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B175" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B176" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B177" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B178" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B181" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B182" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B183" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
+      <c r="I183" s="5"/>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B184" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B185" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H185" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B187" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B188" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B189" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B190" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B193" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B194" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B195" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B196" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B197" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B199" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B200" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5"/>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B201" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B202" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B205" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B206" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B207" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B208" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B209" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G209" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B211" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B212" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="5"/>
+      <c r="E212" s="5"/>
+      <c r="F212" s="5"/>
+      <c r="G212" s="5"/>
+      <c r="H212" s="5"/>
+      <c r="I212" s="5"/>
+    </row>
+    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B213" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I213" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B214" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E214" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B218" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="220" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B220" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="221" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B221" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B222" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
+      <c r="G222" s="5"/>
+      <c r="H222" s="5"/>
+      <c r="I222" s="5"/>
+    </row>
+    <row r="223" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B223" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B224" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B226" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="227" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B227" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5"/>
+      <c r="F227" s="5"/>
+      <c r="G227" s="5"/>
+      <c r="H227" s="5"/>
+      <c r="I227" s="5"/>
+    </row>
+    <row r="228" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B228" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E228" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I228" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B229" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B232" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D232" s="11"/>
+      <c r="E232" s="11"/>
+      <c r="F232" s="11"/>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B233" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D233" s="12"/>
+      <c r="E233" s="12"/>
+      <c r="F233" s="12"/>
+    </row>
+    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B234" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D234" s="12"/>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12"/>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B235" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D235" s="12"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B236" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D236" s="12"/>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B239" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B240" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B241" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="5"/>
+      <c r="G241" s="5"/>
+      <c r="H241" s="5"/>
+      <c r="I241" s="5"/>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B242" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I242" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B243" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I243" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B245" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B246" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" s="5"/>
+      <c r="E246" s="5"/>
+      <c r="F246" s="5"/>
+      <c r="G246" s="5"/>
+      <c r="H246" s="5"/>
+      <c r="I246" s="5"/>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B247" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G247" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I247" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B248" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G248" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H248" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B251" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B252" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B253" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="5"/>
+      <c r="E253" s="5"/>
+      <c r="F253" s="5"/>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
+      <c r="I253" s="5"/>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B254" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I254" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B255" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H255" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B257" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B258" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258" s="5"/>
+      <c r="E258" s="5"/>
+      <c r="F258" s="5"/>
+      <c r="G258" s="5"/>
+      <c r="H258" s="5"/>
+      <c r="I258" s="5"/>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B259" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I259" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B260" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G260" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B263" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B264" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B265" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D265" s="5"/>
+      <c r="E265" s="5"/>
+      <c r="F265" s="5"/>
+      <c r="G265" s="5"/>
+      <c r="H265" s="5"/>
+      <c r="I265" s="5"/>
+    </row>
+    <row r="266" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B266" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I266" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B267" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I267" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="269" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B269" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="270" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B270" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="5"/>
+      <c r="E270" s="5"/>
+      <c r="F270" s="5"/>
+      <c r="G270" s="5"/>
+      <c r="H270" s="5"/>
+      <c r="I270" s="5"/>
+    </row>
+    <row r="271" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B271" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E271" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G271" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H271" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B272" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G272" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H272" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B275" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B276" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B277" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D277" s="5"/>
+      <c r="E277" s="5"/>
+      <c r="F277" s="5"/>
+      <c r="G277" s="5"/>
+      <c r="H277" s="5"/>
+      <c r="I277" s="5"/>
+    </row>
+    <row r="278" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B278" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E278" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B279" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H279" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="281" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B281" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B282" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D282" s="5"/>
+      <c r="E282" s="5"/>
+      <c r="F282" s="5"/>
+      <c r="G282" s="5"/>
+      <c r="H282" s="5"/>
+      <c r="I282" s="5"/>
+    </row>
+    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B283" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G283" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H283" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I283" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B284" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G284" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H284" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C5:I5"/>
+  <mergeCells count="90">
+    <mergeCell ref="C270:I270"/>
+    <mergeCell ref="C277:I277"/>
+    <mergeCell ref="C282:I282"/>
+    <mergeCell ref="C241:I241"/>
+    <mergeCell ref="C246:I246"/>
+    <mergeCell ref="C253:I253"/>
+    <mergeCell ref="C258:I258"/>
+    <mergeCell ref="C265:I265"/>
+    <mergeCell ref="C232:F232"/>
+    <mergeCell ref="C233:F233"/>
+    <mergeCell ref="C234:F234"/>
+    <mergeCell ref="C235:F235"/>
+    <mergeCell ref="C236:F236"/>
+    <mergeCell ref="C200:I200"/>
+    <mergeCell ref="C207:I207"/>
+    <mergeCell ref="C212:I212"/>
+    <mergeCell ref="C222:I222"/>
+    <mergeCell ref="C227:I227"/>
+    <mergeCell ref="C171:I171"/>
+    <mergeCell ref="C176:I176"/>
+    <mergeCell ref="C183:I183"/>
+    <mergeCell ref="C188:I188"/>
+    <mergeCell ref="C195:I195"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="C155:F155"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="C145:F145"/>
+    <mergeCell ref="C146:F146"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="C148:F148"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C140:F140"/>
+    <mergeCell ref="C141:F141"/>
+    <mergeCell ref="C142:F142"/>
+    <mergeCell ref="C143:F143"/>
+    <mergeCell ref="C144:F144"/>
+    <mergeCell ref="C135:F135"/>
+    <mergeCell ref="C136:F136"/>
+    <mergeCell ref="C137:F137"/>
+    <mergeCell ref="C138:F138"/>
+    <mergeCell ref="C139:F139"/>
+    <mergeCell ref="C130:F130"/>
+    <mergeCell ref="C131:F131"/>
+    <mergeCell ref="C132:F132"/>
+    <mergeCell ref="C133:F133"/>
+    <mergeCell ref="C134:F134"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="C129:F129"/>
+    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="C123:F123"/>
+    <mergeCell ref="C124:F124"/>
+    <mergeCell ref="C115:F115"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="C118:F118"/>
+    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="C105:F105"/>
+    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="C107:F107"/>
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="C109:F109"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="C88:I88"/>
+    <mergeCell ref="C93:I93"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C33:I33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/NonameProtocol.xlsx
+++ b/Docs/NonameProtocol.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Development\01_Source\Neurodyne\NRD-W300-V1\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10A77A9-9B09-4D06-88D7-ACEFB1EDD36D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933EFB21-869D-4847-81BA-29DBA0077DC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16770" activeTab="1" xr2:uid="{B534FB32-8458-43B0-8E27-FBD0753503E0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16770" activeTab="2" xr2:uid="{B534FB32-8458-43B0-8E27-FBD0753503E0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="2" r:id="rId1"/>
-    <sheet name="Protocol" sheetId="1" r:id="rId2"/>
+    <sheet name="Revision" sheetId="3" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Protocol" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="209">
   <si>
     <t>BYTE0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,10 +66,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Byte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Control</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -659,10 +656,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Request PST(Pos/Spd/Cur) Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0xA2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -774,6 +767,64 @@
   </si>
   <si>
     <t>0xB1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.08.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>First version</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x01</t>
+  </si>
+  <si>
+    <t>0x01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Request PST(Pos/Spd/Tor) Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -781,7 +832,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,8 +892,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,8 +915,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -879,13 +951,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -910,13 +991,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -925,7 +1009,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1261,178 +1369,294 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21FB4D4-3552-4289-9273-762A01190309}">
+  <dimension ref="B4:D20"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="19" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="50.625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="18"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="18"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="18"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="18"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="18"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="18"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="18"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="18"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="18"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="18"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="18"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="18"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="18"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="18"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="18"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D2795-F3D1-4BB4-870C-3DA182DEFD01}">
   <dimension ref="B4:D20"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="9" customWidth="1"/>
     <col min="5" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>11</v>
+      <c r="D4" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="s">
         <v>62</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>170</v>
+        <v>208</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1441,7 +1665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425A190A-1216-4FBC-A23C-CC9D93A51BC6}">
   <dimension ref="B2:I284"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
@@ -1452,48 +1676,68 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B2" s="14" t="s">
         <v>68</v>
       </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="5" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
     </row>
     <row r="7" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1523,49 +1767,56 @@
     </row>
     <row r="11" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
@@ -1595,58 +1846,71 @@
     </row>
     <row r="16" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
@@ -1676,49 +1940,56 @@
     </row>
     <row r="23" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
@@ -1748,58 +2019,71 @@
     </row>
     <row r="28" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:9" outlineLevel="2" x14ac:dyDescent="0.3"/>
     <row r="30" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="B31" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
     </row>
     <row r="33" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
@@ -1829,49 +2113,56 @@
     </row>
     <row r="35" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="G35" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="H35" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="I35" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="36" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B37" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
     </row>
     <row r="38" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
@@ -1901,59 +2192,72 @@
     </row>
     <row r="40" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="B44" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="15"/>
+      <c r="D44" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B45" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
     </row>
     <row r="47" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
@@ -1983,49 +2287,56 @@
     </row>
     <row r="48" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B48" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="D48" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="G48" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="I48" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="49" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B50" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
     </row>
     <row r="51" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
@@ -2055,59 +2366,72 @@
     </row>
     <row r="53" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B53" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="B57" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="15"/>
+      <c r="D57" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
     </row>
     <row r="58" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B58" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
     </row>
     <row r="59" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
     </row>
     <row r="60" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
@@ -2137,49 +2461,56 @@
     </row>
     <row r="61" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B61" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="E61" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="F61" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="G61" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="I61" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="62" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B63" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
     </row>
     <row r="64" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
     </row>
     <row r="65" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
@@ -2209,59 +2540,72 @@
     </row>
     <row r="66" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B66" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>31</v>
+        <v>57</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="70" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="B70" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
     </row>
     <row r="71" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B71" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
     </row>
     <row r="72" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
     </row>
     <row r="73" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
@@ -2291,49 +2635,56 @@
     </row>
     <row r="74" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B74" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B76" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
     </row>
     <row r="77" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
     </row>
     <row r="78" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
@@ -2363,60 +2714,81 @@
     </row>
     <row r="79" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B79" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>31</v>
+        <v>57</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
     <row r="81" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="8" t="s">
+    <row r="84" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B84" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B87" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="16"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="4" t="s">
@@ -2446,48 +2818,55 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="D90" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="E90" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F90" s="7" t="s">
+      <c r="G90" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G90" s="7" t="s">
+      <c r="H90" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H90" s="7" t="s">
+      <c r="I90" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I90" s="7" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B92" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
@@ -2517,683 +2896,816 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="D95" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="E95" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" s="13"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="1" t="s">
+      <c r="C103" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B104" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B105" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B106" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B107" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B108" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B109" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="13"/>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B110" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B111" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B112" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B113" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B114" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B115" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="13"/>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B116" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B117" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="13"/>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B118" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="13"/>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B119" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B120" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B121" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B122" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B123" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B124" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B125" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B126" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B127" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="13"/>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B128" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13"/>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B129" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="13"/>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B130" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13"/>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B131" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13"/>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B132" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="13"/>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B133" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="13"/>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B134" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B135" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D135" s="13"/>
+      <c r="E135" s="13"/>
+      <c r="F135" s="13"/>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B136" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B137" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
+      <c r="F137" s="13"/>
+      <c r="G137" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B138" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="13"/>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B139" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13"/>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B140" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="13"/>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B141" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="13"/>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B142" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="13"/>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B143" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="13"/>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B144" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
+      <c r="F144" s="13"/>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B145" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13"/>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B146" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="13"/>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B147" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B148" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="13"/>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B149" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B150" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B151" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="13"/>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B154" s="13" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="9" t="s">
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B155" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C155" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="D155" s="12"/>
+      <c r="E155" s="12"/>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B156" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-    </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C104" s="12" t="s">
+      <c r="C156" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="13"/>
+    </row>
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B157" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="12"/>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="12"/>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D106" s="12"/>
-      <c r="E106" s="12"/>
-      <c r="F106" s="12"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D107" s="12"/>
-      <c r="E107" s="12"/>
-      <c r="F107" s="12"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C108" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" s="12"/>
-      <c r="E108" s="12"/>
-      <c r="F108" s="12"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C109" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D109" s="12"/>
-      <c r="E109" s="12"/>
-      <c r="F109" s="12"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D110" s="12"/>
-      <c r="E110" s="12"/>
-      <c r="F110" s="12"/>
-    </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C111" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" s="12"/>
-      <c r="E111" s="12"/>
-      <c r="F111" s="12"/>
-    </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D112" s="12"/>
-      <c r="E112" s="12"/>
-      <c r="F112" s="12"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" s="12"/>
-      <c r="E113" s="12"/>
-      <c r="F113" s="12"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C114" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" s="12"/>
-      <c r="E114" s="12"/>
-      <c r="F114" s="12"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" s="12"/>
-      <c r="E115" s="12"/>
-      <c r="F115" s="12"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" s="12"/>
-      <c r="E116" s="12"/>
-      <c r="F116" s="12"/>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" s="12"/>
-      <c r="E117" s="12"/>
-      <c r="F117" s="12"/>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" s="12"/>
-      <c r="E118" s="12"/>
-      <c r="F118" s="12"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" s="12"/>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12"/>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B120" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D120" s="12"/>
-      <c r="E120" s="12"/>
-      <c r="F120" s="12"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B121" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D121" s="12"/>
-      <c r="E121" s="12"/>
-      <c r="F121" s="12"/>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D122" s="12"/>
-      <c r="E122" s="12"/>
-      <c r="F122" s="12"/>
-    </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" s="12"/>
-      <c r="E123" s="12"/>
-      <c r="F123" s="12"/>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D124" s="12"/>
-      <c r="E124" s="12"/>
-      <c r="F124" s="12"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B125" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C125" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D125" s="12"/>
-      <c r="E125" s="12"/>
-      <c r="F125" s="12"/>
-    </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D126" s="12"/>
-      <c r="E126" s="12"/>
-      <c r="F126" s="12"/>
-    </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D127" s="12"/>
-      <c r="E127" s="12"/>
-      <c r="F127" s="12"/>
-    </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B128" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D128" s="12"/>
-      <c r="E128" s="12"/>
-      <c r="F128" s="12"/>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B129" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D129" s="12"/>
-      <c r="E129" s="12"/>
-      <c r="F129" s="12"/>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B130" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D130" s="12"/>
-      <c r="E130" s="12"/>
-      <c r="F130" s="12"/>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B131" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D131" s="12"/>
-      <c r="E131" s="12"/>
-      <c r="F131" s="12"/>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D132" s="12"/>
-      <c r="E132" s="12"/>
-      <c r="F132" s="12"/>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C133" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D133" s="12"/>
-      <c r="E133" s="12"/>
-      <c r="F133" s="12"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C134" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D134" s="12"/>
-      <c r="E134" s="12"/>
-      <c r="F134" s="12"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C135" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D135" s="12"/>
-      <c r="E135" s="12"/>
-      <c r="F135" s="12"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D136" s="12"/>
-      <c r="E136" s="12"/>
-      <c r="F136" s="12"/>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C137" s="12" t="s">
+      <c r="C157" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D137" s="12"/>
-      <c r="E137" s="12"/>
-      <c r="F137" s="12"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C138" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D138" s="12"/>
-      <c r="E138" s="12"/>
-      <c r="F138" s="12"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B139" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C139" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
-      <c r="F139" s="12"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B140" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D140" s="12"/>
-      <c r="E140" s="12"/>
-      <c r="F140" s="12"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C141" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D141" s="12"/>
-      <c r="E141" s="12"/>
-      <c r="F141" s="12"/>
-    </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C142" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D142" s="12"/>
-      <c r="E142" s="12"/>
-      <c r="F142" s="12"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B143" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D143" s="12"/>
-      <c r="E143" s="12"/>
-      <c r="F143" s="12"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B144" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C144" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D144" s="12"/>
-      <c r="E144" s="12"/>
-      <c r="F144" s="12"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B145" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C145" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D145" s="12"/>
-      <c r="E145" s="12"/>
-      <c r="F145" s="12"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B146" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D146" s="12"/>
-      <c r="E146" s="12"/>
-      <c r="F146" s="12"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B147" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C147" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D147" s="12"/>
-      <c r="E147" s="12"/>
-      <c r="F147" s="12"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B148" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C148" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D148" s="12"/>
-      <c r="E148" s="12"/>
-      <c r="F148" s="12"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B149" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C149" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D149" s="12"/>
-      <c r="E149" s="12"/>
-      <c r="F149" s="12"/>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B150" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C150" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D150" s="12"/>
-      <c r="E150" s="12"/>
-      <c r="F150" s="12"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B151" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D151" s="12"/>
-      <c r="E151" s="12"/>
-      <c r="F151" s="12"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B154" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B155" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C155" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B156" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C156" s="12" t="s">
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
+      <c r="F157" s="13"/>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B160" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D156" s="12"/>
-      <c r="E156" s="12"/>
-      <c r="F156" s="12"/>
-    </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B157" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C157" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D157" s="12"/>
-      <c r="E157" s="12"/>
-      <c r="F157" s="12"/>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B160" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B169" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="B169" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169" s="15"/>
+      <c r="D169" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E169" s="13"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B170" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B170" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="16"/>
+      <c r="D170" s="16"/>
+      <c r="E170" s="16"/>
+      <c r="F170" s="16"/>
+      <c r="G170" s="16"/>
+      <c r="H170" s="16"/>
+      <c r="I170" s="16"/>
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
-      <c r="G171" s="5"/>
-      <c r="H171" s="5"/>
-      <c r="I171" s="5"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="11"/>
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172" s="4" t="s">
@@ -3223,48 +3735,55 @@
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C173" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D173" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D173" s="7" t="s">
+      <c r="E173" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F173" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E173" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F173" s="7" t="s">
+      <c r="G173" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G173" s="7" t="s">
+      <c r="H173" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H173" s="7" t="s">
+      <c r="I173" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I173" s="7" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B175" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B175" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175" s="16"/>
+      <c r="D175" s="16"/>
+      <c r="E175" s="16"/>
+      <c r="F175" s="16"/>
+      <c r="G175" s="16"/>
+      <c r="H175" s="16"/>
+      <c r="I175" s="16"/>
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C176" s="5" t="s">
+      <c r="C176" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
-      <c r="I176" s="5"/>
+      <c r="D176" s="11"/>
+      <c r="E176" s="11"/>
+      <c r="F176" s="11"/>
+      <c r="G176" s="11"/>
+      <c r="H176" s="11"/>
+      <c r="I176" s="11"/>
     </row>
     <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177" s="4" t="s">
@@ -3294,56 +3813,69 @@
     </row>
     <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C178" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D178" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D178" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="E178" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F178" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B181" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C181" s="15"/>
+      <c r="D181" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E181" s="13"/>
+      <c r="F181" s="13"/>
+      <c r="G181" s="13"/>
+      <c r="H181" s="13"/>
+      <c r="I181" s="13"/>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B182" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G178" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H178" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I178" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B181" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B182" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C182" s="16"/>
+      <c r="D182" s="16"/>
+      <c r="E182" s="16"/>
+      <c r="F182" s="16"/>
+      <c r="G182" s="16"/>
+      <c r="H182" s="16"/>
+      <c r="I182" s="16"/>
     </row>
     <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="5"/>
-      <c r="H183" s="5"/>
-      <c r="I183" s="5"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="11"/>
+      <c r="G183" s="11"/>
+      <c r="H183" s="11"/>
+      <c r="I183" s="11"/>
     </row>
     <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
@@ -3373,48 +3905,55 @@
     </row>
     <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G185" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H185" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I185" s="7" t="s">
-        <v>149</v>
+        <v>30</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I185" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B187" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B187" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C187" s="16"/>
+      <c r="D187" s="16"/>
+      <c r="E187" s="16"/>
+      <c r="F187" s="16"/>
+      <c r="G187" s="16"/>
+      <c r="H187" s="16"/>
+      <c r="I187" s="16"/>
     </row>
     <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C188" s="5" t="s">
+      <c r="C188" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
-      <c r="I188" s="5"/>
+      <c r="D188" s="11"/>
+      <c r="E188" s="11"/>
+      <c r="F188" s="11"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="11"/>
+      <c r="I188" s="11"/>
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
@@ -3444,56 +3983,69 @@
     </row>
     <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C190" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D190" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D190" s="7" t="s">
+      <c r="E190" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F190" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E190" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F190" s="4" t="s">
+      <c r="G190" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B193" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C193" s="15"/>
+      <c r="D193" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E193" s="13"/>
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
+      <c r="H193" s="13"/>
+      <c r="I193" s="13"/>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B194" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G190" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H190" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I190" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B193" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B194" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C194" s="16"/>
+      <c r="D194" s="16"/>
+      <c r="E194" s="16"/>
+      <c r="F194" s="16"/>
+      <c r="G194" s="16"/>
+      <c r="H194" s="16"/>
+      <c r="I194" s="16"/>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C195" s="5" t="s">
+      <c r="C195" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
-      <c r="G195" s="5"/>
-      <c r="H195" s="5"/>
-      <c r="I195" s="5"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
@@ -3523,48 +4075,55 @@
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G197" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I197" s="7" t="s">
-        <v>149</v>
+        <v>30</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H197" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I197" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B199" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B199" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" s="16"/>
+      <c r="D199" s="16"/>
+      <c r="E199" s="16"/>
+      <c r="F199" s="16"/>
+      <c r="G199" s="16"/>
+      <c r="H199" s="16"/>
+      <c r="I199" s="16"/>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C200" s="5" t="s">
+      <c r="C200" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
-      <c r="H200" s="5"/>
-      <c r="I200" s="5"/>
+      <c r="D200" s="11"/>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11"/>
+      <c r="I200" s="11"/>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
@@ -3594,56 +4153,69 @@
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D202" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D202" s="7" t="s">
+      <c r="E202" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F202" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E202" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F202" s="4" t="s">
+      <c r="G202" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B205" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C205" s="15"/>
+      <c r="D205" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E205" s="13"/>
+      <c r="F205" s="13"/>
+      <c r="G205" s="13"/>
+      <c r="H205" s="13"/>
+      <c r="I205" s="13"/>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B206" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G202" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I202" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B205" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B206" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C206" s="16"/>
+      <c r="D206" s="16"/>
+      <c r="E206" s="16"/>
+      <c r="F206" s="16"/>
+      <c r="G206" s="16"/>
+      <c r="H206" s="16"/>
+      <c r="I206" s="16"/>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C207" s="5" t="s">
+      <c r="C207" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D207" s="5"/>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
-      <c r="G207" s="5"/>
-      <c r="H207" s="5"/>
-      <c r="I207" s="5"/>
+      <c r="D207" s="11"/>
+      <c r="E207" s="11"/>
+      <c r="F207" s="11"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="11"/>
+      <c r="I207" s="11"/>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
@@ -3673,48 +4245,55 @@
     </row>
     <row r="209" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B209" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C209" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D209" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D209" s="7" t="s">
+      <c r="E209" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F209" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E209" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F209" s="7" t="s">
+      <c r="G209" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G209" s="7" t="s">
+      <c r="H209" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H209" s="7" t="s">
+      <c r="I209" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I209" s="7" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="211" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B211" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B211" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C211" s="16"/>
+      <c r="D211" s="16"/>
+      <c r="E211" s="16"/>
+      <c r="F211" s="16"/>
+      <c r="G211" s="16"/>
+      <c r="H211" s="16"/>
+      <c r="I211" s="16"/>
     </row>
     <row r="212" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C212" s="5" t="s">
+      <c r="C212" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-      <c r="I212" s="5"/>
+      <c r="D212" s="11"/>
+      <c r="E212" s="11"/>
+      <c r="F212" s="11"/>
+      <c r="G212" s="11"/>
+      <c r="H212" s="11"/>
+      <c r="I212" s="11"/>
     </row>
     <row r="213" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
@@ -3744,61 +4323,81 @@
     </row>
     <row r="214" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B214" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C214" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D214" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D214" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="E214" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F214" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B218" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C218" s="20"/>
+      <c r="D218" s="20"/>
+      <c r="E218" s="20"/>
+      <c r="F218" s="20"/>
+      <c r="G218" s="20"/>
+      <c r="H218" s="20"/>
+      <c r="I218" s="20"/>
+    </row>
+    <row r="220" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B220" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C220" s="15"/>
+      <c r="D220" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E220" s="13"/>
+      <c r="F220" s="13"/>
+      <c r="G220" s="13"/>
+      <c r="H220" s="13"/>
+      <c r="I220" s="13"/>
+    </row>
+    <row r="221" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B221" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G214" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I214" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="218" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B218" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="220" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B220" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="221" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B221" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C221" s="16"/>
+      <c r="D221" s="16"/>
+      <c r="E221" s="16"/>
+      <c r="F221" s="16"/>
+      <c r="G221" s="16"/>
+      <c r="H221" s="16"/>
+      <c r="I221" s="16"/>
     </row>
     <row r="222" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C222" s="5" t="s">
+      <c r="C222" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D222" s="5"/>
-      <c r="E222" s="5"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="5"/>
-      <c r="H222" s="5"/>
-      <c r="I222" s="5"/>
+      <c r="D222" s="11"/>
+      <c r="E222" s="11"/>
+      <c r="F222" s="11"/>
+      <c r="G222" s="11"/>
+      <c r="H222" s="11"/>
+      <c r="I222" s="11"/>
     </row>
     <row r="223" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B223" s="4" t="s">
@@ -3828,48 +4427,55 @@
     </row>
     <row r="224" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B224" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B226" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B226" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C226" s="16"/>
+      <c r="D226" s="16"/>
+      <c r="E226" s="16"/>
+      <c r="F226" s="16"/>
+      <c r="G226" s="16"/>
+      <c r="H226" s="16"/>
+      <c r="I226" s="16"/>
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B227" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="C227" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D227" s="5"/>
-      <c r="E227" s="5"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="5"/>
-      <c r="H227" s="5"/>
-      <c r="I227" s="5"/>
+      <c r="D227" s="11"/>
+      <c r="E227" s="11"/>
+      <c r="F227" s="11"/>
+      <c r="G227" s="11"/>
+      <c r="H227" s="11"/>
+      <c r="I227" s="11"/>
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B228" s="4" t="s">
@@ -3899,111 +4505,124 @@
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B229" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C229" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B232" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D232" s="12"/>
+      <c r="E232" s="12"/>
+      <c r="F232" s="12"/>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B233" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C233" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D233" s="13"/>
+      <c r="E233" s="13"/>
+      <c r="F233" s="13"/>
+    </row>
+    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B234" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C234" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D234" s="13"/>
+      <c r="E234" s="13"/>
+      <c r="F234" s="13"/>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B235" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D229" s="4" t="s">
+      <c r="C235" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D235" s="13"/>
+      <c r="E235" s="13"/>
+      <c r="F235" s="13"/>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B236" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C236" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D236" s="13"/>
+      <c r="E236" s="13"/>
+      <c r="F236" s="13"/>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B239" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C239" s="15"/>
+      <c r="D239" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E239" s="13"/>
+      <c r="F239" s="13"/>
+      <c r="G239" s="13"/>
+      <c r="H239" s="13"/>
+      <c r="I239" s="13"/>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B240" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E229" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F229" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G229" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H229" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I229" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="232" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B232" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C232" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D232" s="11"/>
-      <c r="E232" s="11"/>
-      <c r="F232" s="11"/>
-    </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B233" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C233" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D233" s="12"/>
-      <c r="E233" s="12"/>
-      <c r="F233" s="12"/>
-    </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B234" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C234" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D234" s="12"/>
-      <c r="E234" s="12"/>
-      <c r="F234" s="12"/>
-    </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B235" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D235" s="12"/>
-      <c r="E235" s="12"/>
-      <c r="F235" s="12"/>
-    </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B236" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C236" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D236" s="12"/>
-      <c r="E236" s="12"/>
-      <c r="F236" s="12"/>
-    </row>
-    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B239" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B240" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C240" s="16"/>
+      <c r="D240" s="16"/>
+      <c r="E240" s="16"/>
+      <c r="F240" s="16"/>
+      <c r="G240" s="16"/>
+      <c r="H240" s="16"/>
+      <c r="I240" s="16"/>
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B241" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C241" s="5" t="s">
+      <c r="C241" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D241" s="5"/>
-      <c r="E241" s="5"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
-      <c r="H241" s="5"/>
-      <c r="I241" s="5"/>
+      <c r="D241" s="11"/>
+      <c r="E241" s="11"/>
+      <c r="F241" s="11"/>
+      <c r="G241" s="11"/>
+      <c r="H241" s="11"/>
+      <c r="I241" s="11"/>
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B242" s="4" t="s">
@@ -4033,48 +4652,55 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B243" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I243" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B245" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B245" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" s="16"/>
+      <c r="D245" s="16"/>
+      <c r="E245" s="16"/>
+      <c r="F245" s="16"/>
+      <c r="G245" s="16"/>
+      <c r="H245" s="16"/>
+      <c r="I245" s="16"/>
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B246" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C246" s="5" t="s">
+      <c r="C246" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D246" s="5"/>
-      <c r="E246" s="5"/>
-      <c r="F246" s="5"/>
-      <c r="G246" s="5"/>
-      <c r="H246" s="5"/>
-      <c r="I246" s="5"/>
+      <c r="D246" s="11"/>
+      <c r="E246" s="11"/>
+      <c r="F246" s="11"/>
+      <c r="G246" s="11"/>
+      <c r="H246" s="11"/>
+      <c r="I246" s="11"/>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B247" s="4" t="s">
@@ -4104,56 +4730,69 @@
     </row>
     <row r="248" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B248" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G248" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H248" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B251" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C251" s="15"/>
+      <c r="D251" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="C248" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D248" s="4" t="s">
+      <c r="E251" s="13"/>
+      <c r="F251" s="13"/>
+      <c r="G251" s="13"/>
+      <c r="H251" s="13"/>
+      <c r="I251" s="13"/>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B252" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E248" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G248" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H248" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I248" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B251" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B252" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C252" s="16"/>
+      <c r="D252" s="16"/>
+      <c r="E252" s="16"/>
+      <c r="F252" s="16"/>
+      <c r="G252" s="16"/>
+      <c r="H252" s="16"/>
+      <c r="I252" s="16"/>
     </row>
     <row r="253" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B253" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C253" s="5" t="s">
+      <c r="C253" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D253" s="5"/>
-      <c r="E253" s="5"/>
-      <c r="F253" s="5"/>
-      <c r="G253" s="5"/>
-      <c r="H253" s="5"/>
-      <c r="I253" s="5"/>
+      <c r="D253" s="11"/>
+      <c r="E253" s="11"/>
+      <c r="F253" s="11"/>
+      <c r="G253" s="11"/>
+      <c r="H253" s="11"/>
+      <c r="I253" s="11"/>
     </row>
     <row r="254" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B254" s="4" t="s">
@@ -4183,48 +4822,55 @@
     </row>
     <row r="255" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B255" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I255" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="257" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B257" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B257" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C257" s="16"/>
+      <c r="D257" s="16"/>
+      <c r="E257" s="16"/>
+      <c r="F257" s="16"/>
+      <c r="G257" s="16"/>
+      <c r="H257" s="16"/>
+      <c r="I257" s="16"/>
     </row>
     <row r="258" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B258" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C258" s="5" t="s">
+      <c r="C258" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D258" s="5"/>
-      <c r="E258" s="5"/>
-      <c r="F258" s="5"/>
-      <c r="G258" s="5"/>
-      <c r="H258" s="5"/>
-      <c r="I258" s="5"/>
+      <c r="D258" s="11"/>
+      <c r="E258" s="11"/>
+      <c r="F258" s="11"/>
+      <c r="G258" s="11"/>
+      <c r="H258" s="11"/>
+      <c r="I258" s="11"/>
     </row>
     <row r="259" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B259" s="4" t="s">
@@ -4254,56 +4900,69 @@
     </row>
     <row r="260" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B260" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D260" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G260" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B263" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C263" s="15"/>
+      <c r="D263" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E263" s="13"/>
+      <c r="F263" s="13"/>
+      <c r="G263" s="13"/>
+      <c r="H263" s="13"/>
+      <c r="I263" s="13"/>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B264" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E260" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F260" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G260" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H260" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I260" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B263" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B264" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C264" s="16"/>
+      <c r="D264" s="16"/>
+      <c r="E264" s="16"/>
+      <c r="F264" s="16"/>
+      <c r="G264" s="16"/>
+      <c r="H264" s="16"/>
+      <c r="I264" s="16"/>
     </row>
     <row r="265" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B265" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C265" s="5" t="s">
+      <c r="C265" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D265" s="5"/>
-      <c r="E265" s="5"/>
-      <c r="F265" s="5"/>
-      <c r="G265" s="5"/>
-      <c r="H265" s="5"/>
-      <c r="I265" s="5"/>
+      <c r="D265" s="11"/>
+      <c r="E265" s="11"/>
+      <c r="F265" s="11"/>
+      <c r="G265" s="11"/>
+      <c r="H265" s="11"/>
+      <c r="I265" s="11"/>
     </row>
     <row r="266" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B266" s="4" t="s">
@@ -4333,48 +4992,55 @@
     </row>
     <row r="267" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B267" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B269" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B269" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C269" s="16"/>
+      <c r="D269" s="16"/>
+      <c r="E269" s="16"/>
+      <c r="F269" s="16"/>
+      <c r="G269" s="16"/>
+      <c r="H269" s="16"/>
+      <c r="I269" s="16"/>
     </row>
     <row r="270" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B270" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C270" s="5" t="s">
+      <c r="C270" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D270" s="5"/>
-      <c r="E270" s="5"/>
-      <c r="F270" s="5"/>
-      <c r="G270" s="5"/>
-      <c r="H270" s="5"/>
-      <c r="I270" s="5"/>
+      <c r="D270" s="11"/>
+      <c r="E270" s="11"/>
+      <c r="F270" s="11"/>
+      <c r="G270" s="11"/>
+      <c r="H270" s="11"/>
+      <c r="I270" s="11"/>
     </row>
     <row r="271" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B271" s="4" t="s">
@@ -4404,56 +5070,69 @@
     </row>
     <row r="272" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B272" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G272" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H272" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B275" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C275" s="15"/>
+      <c r="D275" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C272" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D272" s="4" t="s">
+      <c r="E275" s="13"/>
+      <c r="F275" s="13"/>
+      <c r="G275" s="13"/>
+      <c r="H275" s="13"/>
+      <c r="I275" s="13"/>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B276" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E272" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F272" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G272" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H272" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I272" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B275" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B276" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C276" s="16"/>
+      <c r="D276" s="16"/>
+      <c r="E276" s="16"/>
+      <c r="F276" s="16"/>
+      <c r="G276" s="16"/>
+      <c r="H276" s="16"/>
+      <c r="I276" s="16"/>
     </row>
     <row r="277" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B277" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C277" s="5" t="s">
+      <c r="C277" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D277" s="5"/>
-      <c r="E277" s="5"/>
-      <c r="F277" s="5"/>
-      <c r="G277" s="5"/>
-      <c r="H277" s="5"/>
-      <c r="I277" s="5"/>
+      <c r="D277" s="11"/>
+      <c r="E277" s="11"/>
+      <c r="F277" s="11"/>
+      <c r="G277" s="11"/>
+      <c r="H277" s="11"/>
+      <c r="I277" s="11"/>
     </row>
     <row r="278" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B278" s="4" t="s">
@@ -4483,48 +5162,55 @@
     </row>
     <row r="279" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B279" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I279" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B281" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B281" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C281" s="16"/>
+      <c r="D281" s="16"/>
+      <c r="E281" s="16"/>
+      <c r="F281" s="16"/>
+      <c r="G281" s="16"/>
+      <c r="H281" s="16"/>
+      <c r="I281" s="16"/>
     </row>
     <row r="282" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B282" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C282" s="5" t="s">
+      <c r="C282" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D282" s="5"/>
-      <c r="E282" s="5"/>
-      <c r="F282" s="5"/>
-      <c r="G282" s="5"/>
-      <c r="H282" s="5"/>
-      <c r="I282" s="5"/>
+      <c r="D282" s="11"/>
+      <c r="E282" s="11"/>
+      <c r="F282" s="11"/>
+      <c r="G282" s="11"/>
+      <c r="H282" s="11"/>
+      <c r="I282" s="11"/>
     </row>
     <row r="283" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B283" s="4" t="s">
@@ -4554,105 +5240,88 @@
     </row>
     <row r="284" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B284" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D284" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E284" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E284" s="7" t="s">
+      <c r="F284" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F284" s="7" t="s">
+      <c r="G284" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G284" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="H284" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I284" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="90">
-    <mergeCell ref="C270:I270"/>
-    <mergeCell ref="C277:I277"/>
-    <mergeCell ref="C282:I282"/>
-    <mergeCell ref="C241:I241"/>
-    <mergeCell ref="C246:I246"/>
-    <mergeCell ref="C253:I253"/>
-    <mergeCell ref="C258:I258"/>
-    <mergeCell ref="C265:I265"/>
-    <mergeCell ref="C232:F232"/>
-    <mergeCell ref="C233:F233"/>
-    <mergeCell ref="C234:F234"/>
-    <mergeCell ref="C235:F235"/>
-    <mergeCell ref="C236:F236"/>
-    <mergeCell ref="C200:I200"/>
-    <mergeCell ref="C207:I207"/>
-    <mergeCell ref="C212:I212"/>
-    <mergeCell ref="C222:I222"/>
-    <mergeCell ref="C227:I227"/>
-    <mergeCell ref="C171:I171"/>
-    <mergeCell ref="C176:I176"/>
-    <mergeCell ref="C183:I183"/>
-    <mergeCell ref="C188:I188"/>
-    <mergeCell ref="C195:I195"/>
-    <mergeCell ref="C150:F150"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="C155:F155"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="C157:F157"/>
-    <mergeCell ref="C145:F145"/>
-    <mergeCell ref="C146:F146"/>
-    <mergeCell ref="C147:F147"/>
-    <mergeCell ref="C148:F148"/>
-    <mergeCell ref="C149:F149"/>
-    <mergeCell ref="C140:F140"/>
-    <mergeCell ref="C141:F141"/>
-    <mergeCell ref="C142:F142"/>
-    <mergeCell ref="C143:F143"/>
-    <mergeCell ref="C144:F144"/>
-    <mergeCell ref="C135:F135"/>
-    <mergeCell ref="C136:F136"/>
-    <mergeCell ref="C137:F137"/>
-    <mergeCell ref="C138:F138"/>
-    <mergeCell ref="C139:F139"/>
-    <mergeCell ref="C130:F130"/>
-    <mergeCell ref="C131:F131"/>
-    <mergeCell ref="C132:F132"/>
-    <mergeCell ref="C133:F133"/>
-    <mergeCell ref="C134:F134"/>
-    <mergeCell ref="C125:F125"/>
-    <mergeCell ref="C126:F126"/>
-    <mergeCell ref="C127:F127"/>
-    <mergeCell ref="C128:F128"/>
-    <mergeCell ref="C129:F129"/>
-    <mergeCell ref="C120:F120"/>
-    <mergeCell ref="C121:F121"/>
-    <mergeCell ref="C122:F122"/>
-    <mergeCell ref="C123:F123"/>
-    <mergeCell ref="C124:F124"/>
-    <mergeCell ref="C115:F115"/>
-    <mergeCell ref="C116:F116"/>
-    <mergeCell ref="C117:F117"/>
-    <mergeCell ref="C118:F118"/>
-    <mergeCell ref="C119:F119"/>
-    <mergeCell ref="C110:F110"/>
-    <mergeCell ref="C111:F111"/>
-    <mergeCell ref="C112:F112"/>
-    <mergeCell ref="C113:F113"/>
-    <mergeCell ref="C114:F114"/>
-    <mergeCell ref="C105:F105"/>
-    <mergeCell ref="C106:F106"/>
-    <mergeCell ref="C107:F107"/>
-    <mergeCell ref="C108:F108"/>
-    <mergeCell ref="C109:F109"/>
+  <mergeCells count="162">
+    <mergeCell ref="B276:I276"/>
+    <mergeCell ref="B281:I281"/>
+    <mergeCell ref="B239:C239"/>
+    <mergeCell ref="D239:I239"/>
+    <mergeCell ref="B240:I240"/>
+    <mergeCell ref="B245:I245"/>
+    <mergeCell ref="B251:C251"/>
+    <mergeCell ref="D251:I251"/>
+    <mergeCell ref="B199:I199"/>
+    <mergeCell ref="B194:I194"/>
+    <mergeCell ref="B205:C205"/>
+    <mergeCell ref="D205:I205"/>
+    <mergeCell ref="B206:I206"/>
+    <mergeCell ref="B170:I170"/>
+    <mergeCell ref="B175:I175"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="D181:I181"/>
+    <mergeCell ref="B182:I182"/>
+    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="B154:I154"/>
+    <mergeCell ref="B160:I160"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="D169:I169"/>
+    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="B92:I92"/>
+    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="B99:I99"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B84:I84"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:I57"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:I70"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="C72:I72"/>
     <mergeCell ref="C77:I77"/>
     <mergeCell ref="B2:I2"/>
@@ -4669,7 +5338,96 @@
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C105:F105"/>
+    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="C107:F107"/>
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="C109:F109"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="C115:F115"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="C118:F118"/>
+    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="C123:F123"/>
+    <mergeCell ref="C124:F124"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="C129:F129"/>
+    <mergeCell ref="C130:F130"/>
+    <mergeCell ref="C131:F131"/>
+    <mergeCell ref="C132:F132"/>
+    <mergeCell ref="C133:F133"/>
+    <mergeCell ref="C134:F134"/>
+    <mergeCell ref="C135:F135"/>
+    <mergeCell ref="C136:F136"/>
+    <mergeCell ref="C137:F137"/>
+    <mergeCell ref="C138:F138"/>
+    <mergeCell ref="C139:F139"/>
+    <mergeCell ref="C140:F140"/>
+    <mergeCell ref="C141:F141"/>
+    <mergeCell ref="C142:F142"/>
+    <mergeCell ref="C143:F143"/>
+    <mergeCell ref="C144:F144"/>
+    <mergeCell ref="C145:F145"/>
+    <mergeCell ref="C146:F146"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="C148:F148"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="C155:F155"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="C171:I171"/>
+    <mergeCell ref="C176:I176"/>
+    <mergeCell ref="C183:I183"/>
+    <mergeCell ref="C188:I188"/>
+    <mergeCell ref="C195:I195"/>
+    <mergeCell ref="B187:I187"/>
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="D193:I193"/>
+    <mergeCell ref="C200:I200"/>
+    <mergeCell ref="C207:I207"/>
+    <mergeCell ref="C212:I212"/>
+    <mergeCell ref="C222:I222"/>
+    <mergeCell ref="C227:I227"/>
+    <mergeCell ref="B211:I211"/>
+    <mergeCell ref="B218:I218"/>
+    <mergeCell ref="B220:C220"/>
+    <mergeCell ref="D220:I220"/>
+    <mergeCell ref="B221:I221"/>
+    <mergeCell ref="B226:I226"/>
+    <mergeCell ref="C232:F232"/>
+    <mergeCell ref="C233:F233"/>
+    <mergeCell ref="C234:F234"/>
+    <mergeCell ref="C235:F235"/>
+    <mergeCell ref="C236:F236"/>
+    <mergeCell ref="C270:I270"/>
+    <mergeCell ref="C277:I277"/>
+    <mergeCell ref="C282:I282"/>
+    <mergeCell ref="C241:I241"/>
+    <mergeCell ref="C246:I246"/>
+    <mergeCell ref="C253:I253"/>
+    <mergeCell ref="C258:I258"/>
+    <mergeCell ref="C265:I265"/>
+    <mergeCell ref="B252:I252"/>
+    <mergeCell ref="B257:I257"/>
+    <mergeCell ref="B263:C263"/>
+    <mergeCell ref="D263:I263"/>
+    <mergeCell ref="B264:I264"/>
+    <mergeCell ref="B269:I269"/>
+    <mergeCell ref="B275:C275"/>
+    <mergeCell ref="D275:I275"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
